--- a/114/11/경량H형강.xlsx
+++ b/114/11/경량H형강.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.251\Project1\html\114\11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1495B24A-53FE-4FD2-8D85-24482F0D316E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5BA189-C08D-4A95-94E7-B84898CBD3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{6DC35BD4-83B4-4D90-A60D-196816A47DBC}"/>
+    <workbookView xWindow="57600" yWindow="0" windowWidth="48600" windowHeight="28200" xr2:uid="{6DC35BD4-83B4-4D90-A60D-196816A47DBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
   <si>
     <t>품명</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -47,10 +47,6 @@
   </si>
   <si>
     <t>단위중량(kg)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>재질</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -293,7 +289,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -704,204 +700,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F457F6-6D9B-4F79-9C0C-045511A231C6}">
-  <dimension ref="A1:E80"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <dimension ref="A1:C80"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.4140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="257" max="257" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="18" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="513" max="513" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="514" max="514" width="18" bestFit="1" customWidth="1"/>
-    <col min="515" max="515" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="769" max="769" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="770" max="770" width="18" bestFit="1" customWidth="1"/>
-    <col min="771" max="771" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1025" max="1025" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="1026" max="1026" width="18" bestFit="1" customWidth="1"/>
-    <col min="1027" max="1027" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1281" max="1281" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="1282" max="1282" width="18" bestFit="1" customWidth="1"/>
-    <col min="1283" max="1283" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1537" max="1537" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="1538" max="1538" width="18" bestFit="1" customWidth="1"/>
-    <col min="1539" max="1539" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1793" max="1793" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="1794" max="1794" width="18" bestFit="1" customWidth="1"/>
-    <col min="1795" max="1795" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2049" max="2049" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="2050" max="2050" width="18" bestFit="1" customWidth="1"/>
-    <col min="2051" max="2051" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2305" max="2305" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="2306" max="2306" width="18" bestFit="1" customWidth="1"/>
-    <col min="2307" max="2307" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2561" max="2561" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="2562" max="2562" width="18" bestFit="1" customWidth="1"/>
-    <col min="2563" max="2563" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2817" max="2817" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="2818" max="2818" width="18" bestFit="1" customWidth="1"/>
-    <col min="2819" max="2819" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3073" max="3073" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="3074" max="3074" width="18" bestFit="1" customWidth="1"/>
-    <col min="3075" max="3075" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3329" max="3329" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="3330" max="3330" width="18" bestFit="1" customWidth="1"/>
-    <col min="3331" max="3331" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3585" max="3585" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="3586" max="3586" width="18" bestFit="1" customWidth="1"/>
-    <col min="3587" max="3587" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3841" max="3841" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="3842" max="3842" width="18" bestFit="1" customWidth="1"/>
-    <col min="3843" max="3843" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4097" max="4097" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4098" max="4098" width="18" bestFit="1" customWidth="1"/>
-    <col min="4099" max="4099" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4353" max="4353" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4354" max="4354" width="18" bestFit="1" customWidth="1"/>
-    <col min="4355" max="4355" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4609" max="4609" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4610" max="4610" width="18" bestFit="1" customWidth="1"/>
-    <col min="4611" max="4611" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4865" max="4865" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4866" max="4866" width="18" bestFit="1" customWidth="1"/>
-    <col min="4867" max="4867" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5121" max="5121" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="5122" max="5122" width="18" bestFit="1" customWidth="1"/>
-    <col min="5123" max="5123" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5377" max="5377" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="5378" max="5378" width="18" bestFit="1" customWidth="1"/>
-    <col min="5379" max="5379" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5633" max="5633" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="5634" max="5634" width="18" bestFit="1" customWidth="1"/>
-    <col min="5635" max="5635" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5889" max="5889" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="5890" max="5890" width="18" bestFit="1" customWidth="1"/>
-    <col min="5891" max="5891" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6145" max="6145" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="6146" max="6146" width="18" bestFit="1" customWidth="1"/>
-    <col min="6147" max="6147" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6401" max="6401" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="6402" max="6402" width="18" bestFit="1" customWidth="1"/>
-    <col min="6403" max="6403" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6657" max="6657" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="6658" max="6658" width="18" bestFit="1" customWidth="1"/>
-    <col min="6659" max="6659" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6913" max="6913" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="6914" max="6914" width="18" bestFit="1" customWidth="1"/>
-    <col min="6915" max="6915" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7169" max="7169" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="7170" max="7170" width="18" bestFit="1" customWidth="1"/>
-    <col min="7171" max="7171" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7425" max="7425" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="7426" max="7426" width="18" bestFit="1" customWidth="1"/>
-    <col min="7427" max="7427" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7681" max="7681" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="7682" max="7682" width="18" bestFit="1" customWidth="1"/>
-    <col min="7683" max="7683" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7937" max="7937" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="7938" max="7938" width="18" bestFit="1" customWidth="1"/>
-    <col min="7939" max="7939" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8193" max="8193" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="8194" max="8194" width="18" bestFit="1" customWidth="1"/>
-    <col min="8195" max="8195" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8449" max="8449" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="8450" max="8450" width="18" bestFit="1" customWidth="1"/>
-    <col min="8451" max="8451" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8705" max="8705" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="8706" max="8706" width="18" bestFit="1" customWidth="1"/>
-    <col min="8707" max="8707" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8961" max="8961" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="8962" max="8962" width="18" bestFit="1" customWidth="1"/>
-    <col min="8963" max="8963" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9217" max="9217" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="9218" max="9218" width="18" bestFit="1" customWidth="1"/>
-    <col min="9219" max="9219" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9473" max="9473" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="9474" max="9474" width="18" bestFit="1" customWidth="1"/>
-    <col min="9475" max="9475" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9729" max="9729" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="9730" max="9730" width="18" bestFit="1" customWidth="1"/>
-    <col min="9731" max="9731" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9985" max="9985" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="9986" max="9986" width="18" bestFit="1" customWidth="1"/>
-    <col min="9987" max="9987" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="10241" max="10241" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="10242" max="10242" width="18" bestFit="1" customWidth="1"/>
-    <col min="10243" max="10243" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="10497" max="10497" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="10498" max="10498" width="18" bestFit="1" customWidth="1"/>
-    <col min="10499" max="10499" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="10753" max="10753" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="10754" max="10754" width="18" bestFit="1" customWidth="1"/>
-    <col min="10755" max="10755" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11009" max="11009" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="11010" max="11010" width="18" bestFit="1" customWidth="1"/>
-    <col min="11011" max="11011" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11265" max="11265" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="11266" max="11266" width="18" bestFit="1" customWidth="1"/>
-    <col min="11267" max="11267" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11521" max="11521" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="11522" max="11522" width="18" bestFit="1" customWidth="1"/>
-    <col min="11523" max="11523" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11777" max="11777" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="11778" max="11778" width="18" bestFit="1" customWidth="1"/>
-    <col min="11779" max="11779" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12033" max="12033" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="12034" max="12034" width="18" bestFit="1" customWidth="1"/>
-    <col min="12035" max="12035" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12289" max="12289" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="12290" max="12290" width="18" bestFit="1" customWidth="1"/>
-    <col min="12291" max="12291" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12545" max="12545" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="12546" max="12546" width="18" bestFit="1" customWidth="1"/>
-    <col min="12547" max="12547" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12801" max="12801" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="12802" max="12802" width="18" bestFit="1" customWidth="1"/>
-    <col min="12803" max="12803" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13057" max="13057" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="13058" max="13058" width="18" bestFit="1" customWidth="1"/>
-    <col min="13059" max="13059" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13313" max="13313" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="13314" max="13314" width="18" bestFit="1" customWidth="1"/>
-    <col min="13315" max="13315" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13569" max="13569" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="13570" max="13570" width="18" bestFit="1" customWidth="1"/>
-    <col min="13571" max="13571" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13825" max="13825" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="13826" max="13826" width="18" bestFit="1" customWidth="1"/>
-    <col min="13827" max="13827" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14081" max="14081" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="14082" max="14082" width="18" bestFit="1" customWidth="1"/>
-    <col min="14083" max="14083" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14337" max="14337" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="14338" max="14338" width="18" bestFit="1" customWidth="1"/>
-    <col min="14339" max="14339" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14593" max="14593" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="14594" max="14594" width="18" bestFit="1" customWidth="1"/>
-    <col min="14595" max="14595" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14849" max="14849" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="14850" max="14850" width="18" bestFit="1" customWidth="1"/>
-    <col min="14851" max="14851" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15105" max="15105" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="15106" max="15106" width="18" bestFit="1" customWidth="1"/>
-    <col min="15107" max="15107" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15361" max="15361" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="15362" max="15362" width="18" bestFit="1" customWidth="1"/>
-    <col min="15363" max="15363" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15617" max="15617" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="15618" max="15618" width="18" bestFit="1" customWidth="1"/>
-    <col min="15619" max="15619" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15873" max="15873" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="15874" max="15874" width="18" bestFit="1" customWidth="1"/>
-    <col min="15875" max="15875" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="16129" max="16129" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="16130" max="16130" width="18" bestFit="1" customWidth="1"/>
-    <col min="16131" max="16131" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="256" max="256" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="257" max="257" width="18" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="512" max="512" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="513" max="513" width="18" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="768" max="768" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="769" max="769" width="18" bestFit="1" customWidth="1"/>
+    <col min="770" max="770" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1024" max="1024" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1025" width="18" bestFit="1" customWidth="1"/>
+    <col min="1026" max="1026" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1280" max="1280" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1281" width="18" bestFit="1" customWidth="1"/>
+    <col min="1282" max="1282" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1536" max="1536" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1537" width="18" bestFit="1" customWidth="1"/>
+    <col min="1538" max="1538" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1792" max="1792" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1793" width="18" bestFit="1" customWidth="1"/>
+    <col min="1794" max="1794" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2048" max="2048" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2049" width="18" bestFit="1" customWidth="1"/>
+    <col min="2050" max="2050" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2304" max="2304" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2305" width="18" bestFit="1" customWidth="1"/>
+    <col min="2306" max="2306" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2560" max="2560" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2561" width="18" bestFit="1" customWidth="1"/>
+    <col min="2562" max="2562" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2816" max="2816" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2817" width="18" bestFit="1" customWidth="1"/>
+    <col min="2818" max="2818" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3072" max="3072" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3073" width="18" bestFit="1" customWidth="1"/>
+    <col min="3074" max="3074" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3328" max="3328" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3329" width="18" bestFit="1" customWidth="1"/>
+    <col min="3330" max="3330" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3584" max="3584" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3585" width="18" bestFit="1" customWidth="1"/>
+    <col min="3586" max="3586" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3840" max="3840" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3841" width="18" bestFit="1" customWidth="1"/>
+    <col min="3842" max="3842" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4096" max="4096" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4097" width="18" bestFit="1" customWidth="1"/>
+    <col min="4098" max="4098" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4352" max="4352" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4353" width="18" bestFit="1" customWidth="1"/>
+    <col min="4354" max="4354" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4608" max="4608" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4609" width="18" bestFit="1" customWidth="1"/>
+    <col min="4610" max="4610" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4864" max="4864" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4865" width="18" bestFit="1" customWidth="1"/>
+    <col min="4866" max="4866" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5120" max="5120" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5121" width="18" bestFit="1" customWidth="1"/>
+    <col min="5122" max="5122" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5376" max="5376" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5377" width="18" bestFit="1" customWidth="1"/>
+    <col min="5378" max="5378" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5632" max="5632" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5633" width="18" bestFit="1" customWidth="1"/>
+    <col min="5634" max="5634" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5888" max="5888" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5889" width="18" bestFit="1" customWidth="1"/>
+    <col min="5890" max="5890" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6144" max="6144" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6145" width="18" bestFit="1" customWidth="1"/>
+    <col min="6146" max="6146" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6400" max="6400" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6401" width="18" bestFit="1" customWidth="1"/>
+    <col min="6402" max="6402" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6656" max="6656" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6657" width="18" bestFit="1" customWidth="1"/>
+    <col min="6658" max="6658" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6912" max="6912" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6913" width="18" bestFit="1" customWidth="1"/>
+    <col min="6914" max="6914" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7168" max="7168" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7169" width="18" bestFit="1" customWidth="1"/>
+    <col min="7170" max="7170" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7424" max="7424" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7425" width="18" bestFit="1" customWidth="1"/>
+    <col min="7426" max="7426" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7680" max="7680" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7681" width="18" bestFit="1" customWidth="1"/>
+    <col min="7682" max="7682" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7936" max="7936" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7937" width="18" bestFit="1" customWidth="1"/>
+    <col min="7938" max="7938" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8192" max="8192" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8193" width="18" bestFit="1" customWidth="1"/>
+    <col min="8194" max="8194" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8448" max="8448" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8449" width="18" bestFit="1" customWidth="1"/>
+    <col min="8450" max="8450" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8704" max="8704" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8705" width="18" bestFit="1" customWidth="1"/>
+    <col min="8706" max="8706" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8960" max="8960" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8961" width="18" bestFit="1" customWidth="1"/>
+    <col min="8962" max="8962" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9216" max="9216" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9217" width="18" bestFit="1" customWidth="1"/>
+    <col min="9218" max="9218" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9472" max="9472" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9473" width="18" bestFit="1" customWidth="1"/>
+    <col min="9474" max="9474" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9728" max="9728" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9729" width="18" bestFit="1" customWidth="1"/>
+    <col min="9730" max="9730" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9984" max="9984" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9985" width="18" bestFit="1" customWidth="1"/>
+    <col min="9986" max="9986" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="10240" max="10240" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10241" width="18" bestFit="1" customWidth="1"/>
+    <col min="10242" max="10242" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="10496" max="10496" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10497" width="18" bestFit="1" customWidth="1"/>
+    <col min="10498" max="10498" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="10752" max="10752" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10753" width="18" bestFit="1" customWidth="1"/>
+    <col min="10754" max="10754" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11008" max="11008" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11009" width="18" bestFit="1" customWidth="1"/>
+    <col min="11010" max="11010" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11264" max="11264" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11265" width="18" bestFit="1" customWidth="1"/>
+    <col min="11266" max="11266" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11520" max="11520" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11521" width="18" bestFit="1" customWidth="1"/>
+    <col min="11522" max="11522" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11776" max="11776" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11777" width="18" bestFit="1" customWidth="1"/>
+    <col min="11778" max="11778" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12032" max="12032" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12033" width="18" bestFit="1" customWidth="1"/>
+    <col min="12034" max="12034" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12288" max="12288" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12289" width="18" bestFit="1" customWidth="1"/>
+    <col min="12290" max="12290" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12544" max="12544" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12545" width="18" bestFit="1" customWidth="1"/>
+    <col min="12546" max="12546" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12800" max="12800" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12801" width="18" bestFit="1" customWidth="1"/>
+    <col min="12802" max="12802" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13056" max="13056" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13057" width="18" bestFit="1" customWidth="1"/>
+    <col min="13058" max="13058" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13312" max="13312" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13313" width="18" bestFit="1" customWidth="1"/>
+    <col min="13314" max="13314" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13568" max="13568" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13569" width="18" bestFit="1" customWidth="1"/>
+    <col min="13570" max="13570" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13824" max="13824" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13825" width="18" bestFit="1" customWidth="1"/>
+    <col min="13826" max="13826" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14080" max="14080" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14081" width="18" bestFit="1" customWidth="1"/>
+    <col min="14082" max="14082" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14336" max="14336" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14337" width="18" bestFit="1" customWidth="1"/>
+    <col min="14338" max="14338" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14592" max="14592" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14593" width="18" bestFit="1" customWidth="1"/>
+    <col min="14594" max="14594" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14848" max="14848" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14849" width="18" bestFit="1" customWidth="1"/>
+    <col min="14850" max="14850" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15104" max="15104" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15105" width="18" bestFit="1" customWidth="1"/>
+    <col min="15106" max="15106" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15360" max="15360" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15361" width="18" bestFit="1" customWidth="1"/>
+    <col min="15362" max="15362" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15616" max="15616" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15617" width="18" bestFit="1" customWidth="1"/>
+    <col min="15618" max="15618" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15872" max="15872" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15873" width="18" bestFit="1" customWidth="1"/>
+    <col min="15874" max="15874" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="16128" max="16128" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16129" width="18" bestFit="1" customWidth="1"/>
+    <col min="16130" max="16130" width="12.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,743 +907,740 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="C2">
         <v>6.4</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>6.5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>5.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>7.6</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>9.35</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>18.2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>8.2100000000000009</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>9.98</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>22.7</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>8.84</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>10.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>13.6</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.6</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>12.9</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>20.3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>27.4</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>10.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>11.9</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>14.1</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>22.7</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>15.4</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>20.8</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>29.8</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>13.1</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>22.3</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>14.9</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>20.2</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>25.9</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>28.6</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>16.7</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>22.5</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>29.4</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38">
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39">
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40">
         <v>46.3</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41">
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C42">
         <v>24.3</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43">
         <v>31.2</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44">
         <v>34.5</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45">
         <v>26.7</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46">
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47">
         <v>41.5</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48">
         <v>55.7</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49">
         <v>28.4</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50">
         <v>36.5</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C51">
         <v>40.4</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C52">
         <v>43.9</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C53">
         <v>41.8</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54">
         <v>46.3</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55">
         <v>60.4</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56">
         <v>43.5</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C57">
         <v>62.7</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C58">
         <v>77.5</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="1"/>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" s="1"/>
       <c r="B60" s="3"/>
       <c r="C60" s="4"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" s="1"/>
       <c r="B61" s="3"/>
       <c r="C61" s="4"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="1"/>
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="1"/>
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="1"/>
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" s="1"/>
       <c r="B65" s="3"/>
       <c r="C65" s="4"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="1"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" s="1"/>
       <c r="B67" s="3"/>
       <c r="C67" s="4"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" s="1"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="1"/>
       <c r="B69" s="3"/>
       <c r="C69" s="4"/>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" s="1"/>
       <c r="B70" s="3"/>
       <c r="C70" s="4"/>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" s="1"/>
       <c r="B71" s="3"/>
       <c r="C71" s="4"/>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" s="1"/>
       <c r="B72" s="3"/>
       <c r="C72" s="4"/>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" s="1"/>
       <c r="B73" s="3"/>
       <c r="C73" s="4"/>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" s="1"/>
       <c r="B74" s="3"/>
       <c r="C74" s="4"/>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75" s="1"/>
       <c r="B75" s="3"/>
       <c r="C75" s="4"/>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76" s="1"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4"/>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" s="1"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" s="1"/>
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" s="1"/>
       <c r="B79" s="3"/>
       <c r="C79" s="4"/>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" s="1"/>
       <c r="B80" s="3"/>
       <c r="C80" s="4"/>
